--- a/img/programs/Proj. Library.xlsx
+++ b/img/programs/Proj. Library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qingyanzhu/Library/Containers/com.tencent.xinWeChat/Data/Library/Application Support/com.tencent.xinWeChat/2.0b4.0.9/5da5d6191b7f607752fbc98c324a3e7d/Message/MessageTemp/cc27149c6589ae623998c519f954631c/File/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553DA4DD-51FA-724D-98EB-30A62671D497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB7B95D-3666-004D-A3CA-6DE5CFDE2218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11140" yWindow="3020" windowWidth="41620" windowHeight="24300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4460" yWindow="1120" windowWidth="41620" windowHeight="24300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="项目" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="437">
   <si>
     <t>Project #</t>
   </si>
@@ -1269,18 +1269,100 @@
   </si>
   <si>
     <t>The Hague, The Netherlands</t>
+  </si>
+  <si>
+    <t>设计</t>
+  </si>
+  <si>
+    <t>Designer</t>
+  </si>
+  <si>
+    <t>（Field Trip）</t>
+  </si>
+  <si>
+    <t>BIG （习作）</t>
+  </si>
+  <si>
+    <t>（习作）</t>
+  </si>
+  <si>
+    <t>BIG（Field Trip）</t>
+  </si>
+  <si>
+    <t>Zhaoyang Architects（Field Trip）</t>
+  </si>
+  <si>
+    <t>FENG Jizhong（Field Trip）</t>
+  </si>
+  <si>
+    <t>Elepheno Architects（Field Trip）</t>
+  </si>
+  <si>
+    <t>/Jahn（Field Trip）</t>
+  </si>
+  <si>
+    <t>Studio Libeskind（Field Trip）</t>
+  </si>
+  <si>
+    <t>Foster + Partners（Field Trip）</t>
+  </si>
+  <si>
+    <t>MVRDV（Field Trip）</t>
+  </si>
+  <si>
+    <t>Zaha Hadid Architects（Field Trip）</t>
+  </si>
+  <si>
+    <t>Hendrik Petrus Berlage（Field Trip）</t>
+  </si>
+  <si>
+    <t>Hendrik Petrus Berlage（习作）</t>
+  </si>
+  <si>
+    <t>Zaha Hadid Architects（习作）</t>
+  </si>
+  <si>
+    <t>MVRDV（习作）</t>
+  </si>
+  <si>
+    <t>Foster + Partners（习作）</t>
+  </si>
+  <si>
+    <t>Studio Libeskind（习作）</t>
+  </si>
+  <si>
+    <t>/Jahn（习作）</t>
+  </si>
+  <si>
+    <t>BIG（习作）</t>
+  </si>
+  <si>
+    <t>筑象建筑设计工作室（习作）</t>
+  </si>
+  <si>
+    <t>冯纪忠（习作）</t>
+  </si>
+  <si>
+    <t>赵扬建筑工作室（习作）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1397,24 +1479,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1422,7 +1504,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1432,26 +1514,26 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1460,12 +1542,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5215,17 +5298,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B46A21C-922E-F146-9075-22630F664DEC}">
-  <dimension ref="B1:F16"/>
+  <dimension ref="B1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="47.33203125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
+    <col min="6" max="7" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7" s="1" customFormat="1" ht="26" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
@@ -5239,10 +5322,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>2015</v>
       </c>
@@ -5255,8 +5341,14 @@
       <c r="E2" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>375</v>
       </c>
@@ -5269,8 +5361,14 @@
       <c r="E3" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>2023</v>
       </c>
@@ -5283,8 +5381,14 @@
       <c r="E4" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2025</v>
       </c>
@@ -5297,8 +5401,14 @@
       <c r="E5" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2025</v>
       </c>
@@ -5311,8 +5421,14 @@
       <c r="E6" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2026</v>
       </c>
@@ -5325,8 +5441,14 @@
       <c r="E7" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>434</v>
+      </c>
+      <c r="G7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2026</v>
       </c>
@@ -5339,8 +5461,14 @@
       <c r="E8" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>416</v>
+      </c>
+      <c r="G8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>2016</v>
       </c>
@@ -5353,8 +5481,14 @@
       <c r="E9" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>416</v>
+      </c>
+      <c r="G9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2023</v>
       </c>
@@ -5367,8 +5501,14 @@
       <c r="E10" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>433</v>
+      </c>
+      <c r="G10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2022</v>
       </c>
@@ -5381,8 +5521,14 @@
       <c r="E11" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>432</v>
+      </c>
+      <c r="G11" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>2022</v>
       </c>
@@ -5395,8 +5541,14 @@
       <c r="E12" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>431</v>
+      </c>
+      <c r="G12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>2022</v>
       </c>
@@ -5409,8 +5561,14 @@
       <c r="E13" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>430</v>
+      </c>
+      <c r="G13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>2023</v>
       </c>
@@ -5423,8 +5581,14 @@
       <c r="E14" s="29" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" ht="24" x14ac:dyDescent="0.35">
+      <c r="F14" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="24" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>2022</v>
       </c>
@@ -5437,8 +5601,14 @@
       <c r="E15" s="29" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>2023</v>
       </c>
@@ -5450,6 +5620,12 @@
       </c>
       <c r="E16" s="29" t="s">
         <v>411</v>
+      </c>
+      <c r="F16" t="s">
+        <v>427</v>
+      </c>
+      <c r="G16" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
